--- a/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
@@ -766,10 +766,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -821,22 +821,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -983,22 +983,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>01/28/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Health Choice Arizona</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Health Choice Arizona</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>01/28/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -1100,22 +1100,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>01/28/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Health Choice Arizona</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Health Choice Arizona</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>01/28/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -1221,22 +1221,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1340,22 +1340,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1459,22 +1459,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Banner University Family Care / ACC (AHCCS Complete Care)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Banner University Family Care / ACC (AHCCS Complete Care)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>01/21/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1574,22 +1574,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>01/22/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>01/22/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1683,22 +1683,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>01/22/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>01/22/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>01/28/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>01/28/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1915,22 +1915,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2028,22 +2028,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2145,22 +2145,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2375,22 +2375,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -2488,22 +2488,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>01/14/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>01/14/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -2601,22 +2601,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>01/21/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -2718,22 +2718,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>01/21/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2839,22 +2839,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>01/22/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>TRIADA GAP BENEFITS</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>TRIADA GAP BENEFITS</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>01/22/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -2958,22 +2958,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>01/27/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>01/27/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -3075,22 +3075,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>01/27/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>01/27/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -3192,22 +3192,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>01/27/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>01/27/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -3309,22 +3309,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>01/29/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>LIEN 05</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>01/29/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -3426,22 +3426,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>01/14/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>01/14/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -3539,22 +3539,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>01/14/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>01/14/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -3652,22 +3652,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>01/23/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>01/23/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -3759,22 +3759,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>01/23/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>01/23/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -3895,10 +3895,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -3950,22 +3950,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -4112,22 +4112,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>CIGNA MEDICARE SUPPLEMENT INSURANCE</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -4233,22 +4233,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -4350,22 +4350,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -4471,22 +4471,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -4592,22 +4592,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>01/29/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Bankers Life Colonial Penn Life</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>01/29/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -4721,22 +4721,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Tricare for Life (All Regions)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -4856,22 +4856,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Allwell - All States (Centene)</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -5012,10 +5012,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -5067,22 +5067,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -5233,22 +5233,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -5364,22 +5364,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -5491,22 +5491,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -5614,22 +5614,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -5749,22 +5749,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -5876,22 +5876,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -6134,22 +6134,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Aetna Senior Supplemental (AESSI) - Secondary Only 62118</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Aetna Senior Supplemental (AESSI) - Secondary Only 62118</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -6261,22 +6261,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -6388,22 +6388,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -6523,22 +6523,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -6662,22 +6662,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -6797,22 +6797,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -6928,22 +6928,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -7059,22 +7059,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Unicare Life and Health Insurance (Anthem)</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -7190,22 +7190,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -7329,22 +7329,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -7464,22 +7464,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -7861,22 +7861,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -7992,22 +7992,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>01/19/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -8119,22 +8119,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Bankers Life Colonial Penn Life</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -8250,22 +8250,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Bankers Life Colonial Penn Life</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -8381,22 +8381,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>Bankers Life Colonial Penn Life</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -8516,22 +8516,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Bankers Life Colonial Penn Life</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -8655,22 +8655,22 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Bankers Life Colonial Penn Life</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -8786,22 +8786,22 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Bankers Life Colonial Penn Life</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -8917,22 +8917,22 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -9052,22 +9052,22 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -9187,22 +9187,22 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -9314,22 +9314,22 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -9447,22 +9447,22 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -9576,22 +9576,22 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -9701,22 +9701,22 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -9830,22 +9830,22 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -9959,22 +9959,22 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -10084,22 +10084,22 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -10217,22 +10217,22 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -10346,22 +10346,22 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -10471,22 +10471,22 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -10600,22 +10600,22 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -10729,22 +10729,22 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -10862,22 +10862,22 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -10991,22 +10991,22 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -11116,22 +11116,22 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -11249,22 +11249,22 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -11368,22 +11368,22 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -11483,22 +11483,22 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -11717,22 +11717,22 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -11840,22 +11840,22 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
@@ -11963,22 +11963,22 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -12111,10 +12111,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -12328,22 +12328,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>01/15/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>01/15/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -12445,22 +12445,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>CIGNA</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>CIGNA</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -12566,22 +12566,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -12681,22 +12681,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>01/13/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>01/13/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -12798,22 +12798,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>01/14/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>01/14/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -12919,22 +12919,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>01/23/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>01/23/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -13042,22 +13042,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>01/23/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>01/23/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -13159,22 +13159,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>01/23/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>01/23/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -13278,22 +13278,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>01/23/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>01/23/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -13401,22 +13401,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Tricare West</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Tricare West</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>01/26/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -13545,10 +13545,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -13600,22 +13600,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -13766,22 +13766,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -13883,22 +13883,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -14004,22 +14004,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>01/13/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Cigna Medicare Advantage</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Cigna Medicare Advantage</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>01/13/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -14121,22 +14121,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>01/14/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Cigna Medicare Advantage</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Cigna Medicare Advantage</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>01/14/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -14246,22 +14246,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>01/15/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>01/15/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -14367,22 +14367,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>01/21/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -14484,22 +14484,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>01/29/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>01/29/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">

--- a/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
@@ -1037,40 +1037,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="5" t="n">
-        <v>566830437</v>
+        <v>545752977</v>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>HF453012792</t>
+          <t>HF512527332</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>01/28/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Health Choice Arizona</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Health Choice Arizona</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K2" s="4" t="n"/>
@@ -1079,16 +1083,16 @@
         <v/>
       </c>
       <c r="M2" s="7" t="n">
-        <v>46262</v>
+        <v>46396</v>
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>7 months</t>
+          <t>365 days</t>
         </is>
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>HEALTH CHOICE MEDICAID</t>
+          <t>MEDICARE</t>
         </is>
       </c>
       <c r="P2" s="6" t="n"/>
@@ -1098,34 +1102,36 @@
         <v>1</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U2" s="8" t="n">
-        <v>0</v>
+        <v>886.78</v>
       </c>
       <c r="V2" s="8" t="n">
-        <v>0</v>
+        <v>111.85</v>
       </c>
       <c r="W2" s="6" t="inlineStr">
         <is>
-          <t>06/25/2026</t>
+          <t>02/18/2026</t>
         </is>
       </c>
       <c r="X2" s="8" t="n">
-        <v>396.27</v>
+        <v>31.35</v>
       </c>
       <c r="Y2" s="5" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="Z2" s="6" t="inlineStr">
         <is>
-          <t>F411</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA2" s="6" t="n"/>
       <c r="AB2" s="6" t="n"/>
       <c r="AC2" s="6" t="n"/>
-      <c r="AD2" s="5" t="n"/>
+      <c r="AD2" s="5" t="n">
+        <v>550866078</v>
+      </c>
       <c r="AE2" s="6" t="inlineStr">
         <is>
           <t>LEATHEM, JARRETT</t>
@@ -1133,12 +1139,12 @@
       </c>
       <c r="AF2" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG2" s="6" t="inlineStr">
         <is>
-          <t>06/15/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="AH2" s="6" t="inlineStr">
@@ -1146,50 +1152,50 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI2" s="9" t="inlineStr">
-        <is>
-          <t>7 months because Health Choice is the primary payer here (6 months when it is not). Counted in calendar months.</t>
-        </is>
-      </c>
+      <c r="AI2" s="9" t="n"/>
       <c r="AJ2" s="5" t="n">
-        <v>939</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="5" t="n">
-        <v>566830437</v>
+        <v>545752977</v>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>HF453012792</t>
+          <t>HF512527332</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>01/28/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Health Choice Arizona</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Health Choice Arizona</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K3" s="4" t="n"/>
@@ -1198,53 +1204,55 @@
         <v/>
       </c>
       <c r="M3" s="7" t="n">
-        <v>46262</v>
+        <v>46396</v>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>7 months</t>
+          <t>365 days</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>HEALTH CHOICE MEDICAID</t>
+          <t>MEDICARE</t>
         </is>
       </c>
       <c r="P3" s="6" t="n"/>
       <c r="Q3" s="6" t="n"/>
       <c r="R3" s="6" t="n"/>
       <c r="S3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>976.64</v>
+        <v>792.54</v>
       </c>
       <c r="U3" s="8" t="n">
-        <v>0</v>
+        <v>682.6</v>
       </c>
       <c r="V3" s="8" t="n">
-        <v>0</v>
+        <v>85.87</v>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>06/25/2026</t>
+          <t>02/18/2026</t>
         </is>
       </c>
       <c r="X3" s="8" t="n">
-        <v>976.64</v>
+        <v>24.07</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="Z3" s="6" t="inlineStr">
         <is>
-          <t>F411</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA3" s="6" t="n"/>
       <c r="AB3" s="6" t="n"/>
       <c r="AC3" s="6" t="n"/>
-      <c r="AD3" s="5" t="n"/>
+      <c r="AD3" s="5" t="n">
+        <v>550866078</v>
+      </c>
       <c r="AE3" s="6" t="inlineStr">
         <is>
           <t>LEATHEM, JARRETT</t>
@@ -1252,12 +1260,12 @@
       </c>
       <c r="AF3" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG3" s="6" t="inlineStr">
         <is>
-          <t>06/15/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="AH3" s="6" t="inlineStr">
@@ -1265,13 +1273,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI3" s="9" t="inlineStr">
-        <is>
-          <t>7 months because Health Choice is the primary payer here (6 months when it is not). Counted in calendar months.</t>
-        </is>
-      </c>
+      <c r="AI3" s="9" t="n"/>
       <c r="AJ3" s="5" t="n">
-        <v>940</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4">
@@ -1283,21 +1287,21 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="5" t="n">
-        <v>545752977</v>
+        <v>547309790</v>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>HF512527332</t>
+          <t>HF529978681</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/21/2026</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Banner University Family Care / ACC (AHCCS Complete Care)</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -1307,12 +1311,12 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Banner University Family Care / ACC (AHCCS Complete Care)</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K4" s="4" t="n"/>
@@ -1321,7 +1325,7 @@
         <v/>
       </c>
       <c r="M4" s="7" t="n">
-        <v>46396</v>
+        <v>46408</v>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
@@ -1340,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>1029.98</v>
+        <v>976.64</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>886.78</v>
+        <v>846.88</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>111.85</v>
+        <v>101.35</v>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
@@ -1354,35 +1358,35 @@
         </is>
       </c>
       <c r="X4" s="8" t="n">
-        <v>31.35</v>
+        <v>28.41</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="Z4" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F4322</t>
         </is>
       </c>
       <c r="AA4" s="6" t="n"/>
       <c r="AB4" s="6" t="n"/>
       <c r="AC4" s="6" t="n"/>
       <c r="AD4" s="5" t="n">
-        <v>550866078</v>
+        <v>550866344</v>
       </c>
       <c r="AE4" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF4" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG4" s="6" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="AH4" s="6" t="inlineStr">
@@ -1392,33 +1396,29 @@
       </c>
       <c r="AI4" s="9" t="n"/>
       <c r="AJ4" s="5" t="n">
-        <v>259</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="5" t="n">
-        <v>545752977</v>
+        <v>555619522</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>HF512527332</t>
+          <t>HF436968693</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/22/2026</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -1442,7 +1442,7 @@
         <v/>
       </c>
       <c r="M5" s="7" t="n">
-        <v>46396</v>
+        <v>46409</v>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
@@ -1458,27 +1458,23 @@
       <c r="Q5" s="6" t="n"/>
       <c r="R5" s="6" t="n"/>
       <c r="S5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>792.54</v>
+        <v>396.27</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>682.6</v>
+        <v>0</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>85.87</v>
-      </c>
-      <c r="W5" s="6" t="inlineStr">
-        <is>
-          <t>02/18/2026</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W5" s="6" t="n"/>
       <c r="X5" s="8" t="n">
-        <v>24.07</v>
+        <v>396.27</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="Z5" s="6" t="inlineStr">
         <is>
@@ -1488,22 +1484,20 @@
       <c r="AA5" s="6" t="n"/>
       <c r="AB5" s="6" t="n"/>
       <c r="AC5" s="6" t="n"/>
-      <c r="AD5" s="5" t="n">
-        <v>550866078</v>
-      </c>
+      <c r="AD5" s="5" t="n"/>
       <c r="AE5" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF5" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG5" s="6" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="AH5" s="6" t="inlineStr">
@@ -1513,33 +1507,29 @@
       </c>
       <c r="AI5" s="9" t="n"/>
       <c r="AJ5" s="5" t="n">
-        <v>260</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="5" t="n">
-        <v>547309790</v>
+        <v>555619522</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>HF529978681</t>
+          <t>HF436968693</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>01/21/2026</t>
+          <t>01/22/2026</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Banner University Family Care / ACC (AHCCS Complete Care)</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -1549,12 +1539,12 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Banner University Family Care / ACC (AHCCS Complete Care)</t>
+          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K6" s="4" t="n"/>
@@ -1563,7 +1553,7 @@
         <v/>
       </c>
       <c r="M6" s="7" t="n">
-        <v>46408</v>
+        <v>46409</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
@@ -1582,39 +1572,37 @@
         <v>1</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>976.64</v>
+        <v>1029.98</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>846.88</v>
+        <v>0</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>101.35</v>
+        <v>0</v>
       </c>
       <c r="W6" s="6" t="inlineStr">
         <is>
-          <t>02/18/2026</t>
+          <t>04/17/2026</t>
         </is>
       </c>
       <c r="X6" s="8" t="n">
-        <v>28.41</v>
+        <v>1029.98</v>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Z6" s="6" t="inlineStr">
         <is>
-          <t>F4322</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA6" s="6" t="n"/>
       <c r="AB6" s="6" t="n"/>
       <c r="AC6" s="6" t="n"/>
-      <c r="AD6" s="5" t="n">
-        <v>550866344</v>
-      </c>
+      <c r="AD6" s="5" t="n"/>
       <c r="AE6" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF6" s="6" t="inlineStr">
@@ -1634,44 +1622,48 @@
       </c>
       <c r="AI6" s="9" t="n"/>
       <c r="AJ6" s="5" t="n">
-        <v>168</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="5" t="n">
-        <v>555619522</v>
+        <v>547756234</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>HF436968693</t>
+          <t>HF411566237</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>01/22/2026</t>
+          <t>01/28/2026</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
+          <t>Blue Cross Blue Shield of Arizona</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
+          <t>Blue Cross Blue Shield of Arizona</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K7" s="4" t="n"/>
@@ -1680,7 +1672,7 @@
         <v/>
       </c>
       <c r="M7" s="7" t="n">
-        <v>46409</v>
+        <v>46415</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
@@ -1699,43 +1691,49 @@
         <v>1</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>0</v>
+        <v>844.25</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="6" t="n"/>
+        <v>103.98</v>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
+          <t>02/19/2026</t>
+        </is>
+      </c>
       <c r="X7" s="8" t="n">
-        <v>396.27</v>
+        <v>28.41</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="Z7" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F411</t>
         </is>
       </c>
       <c r="AA7" s="6" t="n"/>
       <c r="AB7" s="6" t="n"/>
       <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="5" t="n"/>
+      <c r="AD7" s="5" t="n">
+        <v>550865889</v>
+      </c>
       <c r="AE7" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>BURGHER, ABRAM</t>
         </is>
       </c>
       <c r="AF7" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG7" s="6" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="AH7" s="6" t="inlineStr">
@@ -1745,7 +1743,7 @@
       </c>
       <c r="AI7" s="9" t="n"/>
       <c r="AJ7" s="5" t="n">
-        <v>652</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8">
@@ -1753,36 +1751,36 @@
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="5" t="n">
-        <v>555619522</v>
+        <v>545332485</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>HF436968693</t>
+          <t>HF532613047</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>01/22/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>United Healthcare</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>United Healthcare</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K8" s="4" t="n"/>
@@ -1791,16 +1789,16 @@
         <v/>
       </c>
       <c r="M8" s="7" t="n">
-        <v>46409</v>
+        <v>46118</v>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>365 days</t>
+          <t>90 days</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>MEDICARE</t>
+          <t>UHC COMMERCIAL</t>
         </is>
       </c>
       <c r="P8" s="6" t="n"/>
@@ -1810,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U8" s="8" t="n">
         <v>0</v>
@@ -1820,14 +1818,14 @@
       </c>
       <c r="W8" s="6" t="inlineStr">
         <is>
-          <t>04/17/2026</t>
+          <t>04/30/2026</t>
         </is>
       </c>
       <c r="X8" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="Z8" s="6" t="inlineStr">
         <is>
@@ -1845,12 +1843,12 @@
       </c>
       <c r="AF8" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG8" s="6" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="AH8" s="6" t="inlineStr">
@@ -1860,48 +1858,44 @@
       </c>
       <c r="AI8" s="9" t="n"/>
       <c r="AJ8" s="5" t="n">
-        <v>653</v>
+        <v>627</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="n"/>
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="5" t="n">
-        <v>547756234</v>
+        <v>545484752</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>HF411566237</t>
+          <t>HF331360774</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>01/28/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K9" s="4" t="n"/>
@@ -1910,16 +1904,16 @@
         <v/>
       </c>
       <c r="M9" s="7" t="n">
-        <v>46415</v>
+        <v>46119</v>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>365 days</t>
+          <t>90 days</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>MEDICARE</t>
+          <t>BCBS</t>
         </is>
       </c>
       <c r="P9" s="6" t="n"/>
@@ -1929,39 +1923,37 @@
         <v>1</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U9" s="8" t="n">
-        <v>844.25</v>
+        <v>0</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>103.98</v>
+        <v>0</v>
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="X9" s="8" t="n">
-        <v>28.41</v>
+        <v>396.27</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
-          <t>F411</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA9" s="6" t="n"/>
       <c r="AB9" s="6" t="n"/>
       <c r="AC9" s="6" t="n"/>
-      <c r="AD9" s="5" t="n">
-        <v>550865889</v>
-      </c>
+      <c r="AD9" s="5" t="n"/>
       <c r="AE9" s="6" t="inlineStr">
         <is>
-          <t>BURGHER, ABRAM</t>
+          <t>SARKAR, AWNIK</t>
         </is>
       </c>
       <c r="AF9" s="6" t="inlineStr">
@@ -1979,9 +1971,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI9" s="9" t="n"/>
+      <c r="AI9" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
+        </is>
+      </c>
       <c r="AJ9" s="5" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -1989,26 +1985,26 @@
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="5" t="n">
-        <v>545332485</v>
+        <v>545484752</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>HF532613047</t>
+          <t>HF331360774</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>United Healthcare</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>United Healthcare</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -2018,7 +2014,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K10" s="4" t="n"/>
@@ -2027,7 +2023,7 @@
         <v/>
       </c>
       <c r="M10" s="7" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
@@ -2036,7 +2032,7 @@
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>UHC COMMERCIAL</t>
+          <t>BCBS</t>
         </is>
       </c>
       <c r="P10" s="6" t="n"/>
@@ -2046,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U10" s="8" t="n">
         <v>0</v>
@@ -2056,14 +2052,14 @@
       </c>
       <c r="W10" s="6" t="inlineStr">
         <is>
-          <t>04/30/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="X10" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
@@ -2076,7 +2072,7 @@
       <c r="AD10" s="5" t="n"/>
       <c r="AE10" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>SARKAR, AWNIK</t>
         </is>
       </c>
       <c r="AF10" s="6" t="inlineStr">
@@ -2094,9 +2090,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI10" s="9" t="n"/>
+      <c r="AI10" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
+        </is>
+      </c>
       <c r="AJ10" s="5" t="n">
-        <v>627</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -2104,26 +2104,26 @@
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="5" t="n">
-        <v>545484752</v>
+        <v>545748574</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>HF331360774</t>
+          <t>HF537684538</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>United Healthcare</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>United Healthcare</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -2142,7 +2142,7 @@
         <v/>
       </c>
       <c r="M11" s="7" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>BCBS</t>
+          <t>UHC COMMERCIAL</t>
         </is>
       </c>
       <c r="P11" s="6" t="n"/>
@@ -2171,14 +2171,14 @@
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>04/29/2026</t>
         </is>
       </c>
       <c r="X11" s="8" t="n">
         <v>396.27</v>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       <c r="AD11" s="5" t="n"/>
       <c r="AE11" s="6" t="inlineStr">
         <is>
-          <t>SARKAR, AWNIK</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF11" s="6" t="inlineStr">
@@ -2209,13 +2209,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI11" s="9" t="inlineStr">
-        <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
-        </is>
-      </c>
+      <c r="AI11" s="9" t="n"/>
       <c r="AJ11" s="5" t="n">
-        <v>119</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
@@ -2223,26 +2219,26 @@
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="5" t="n">
-        <v>545484752</v>
+        <v>545748574</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>HF331360774</t>
+          <t>HF537684538</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>United Healthcare</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>United Healthcare</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -2261,7 +2257,7 @@
         <v/>
       </c>
       <c r="M12" s="7" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
@@ -2270,7 +2266,7 @@
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>BCBS</t>
+          <t>UHC COMMERCIAL</t>
         </is>
       </c>
       <c r="P12" s="6" t="n"/>
@@ -2290,14 +2286,14 @@
       </c>
       <c r="W12" s="6" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>04/29/2026</t>
         </is>
       </c>
       <c r="X12" s="8" t="n">
         <v>1029.98</v>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
@@ -2310,7 +2306,7 @@
       <c r="AD12" s="5" t="n"/>
       <c r="AE12" s="6" t="inlineStr">
         <is>
-          <t>SARKAR, AWNIK</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF12" s="6" t="inlineStr">
@@ -2328,13 +2324,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI12" s="9" t="inlineStr">
-        <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
-        </is>
-      </c>
+      <c r="AI12" s="9" t="n"/>
       <c r="AJ12" s="5" t="n">
-        <v>126</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -2342,26 +2334,26 @@
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="5" t="n">
-        <v>545748574</v>
+        <v>556348109</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>HF537684538</t>
+          <t>HF434792716</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/14/2026</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>United Healthcare</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>United Healthcare</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -2371,7 +2363,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K13" s="4" t="n"/>
@@ -2380,7 +2372,7 @@
         <v/>
       </c>
       <c r="M13" s="7" t="n">
-        <v>46121</v>
+        <v>46126</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
@@ -2389,7 +2381,7 @@
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>UHC COMMERCIAL</t>
+          <t>OPTUM</t>
         </is>
       </c>
       <c r="P13" s="6" t="n"/>
@@ -2399,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U13" s="8" t="n">
         <v>0</v>
@@ -2409,18 +2401,18 @@
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>04/29/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="X13" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Z13" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA13" s="6" t="n"/>
@@ -2429,12 +2421,12 @@
       <c r="AD13" s="5" t="n"/>
       <c r="AE13" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF13" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG13" s="6" t="inlineStr">
@@ -2449,7 +2441,7 @@
       </c>
       <c r="AI13" s="9" t="n"/>
       <c r="AJ13" s="5" t="n">
-        <v>51</v>
+        <v>715</v>
       </c>
     </row>
     <row r="14">
@@ -2457,36 +2449,36 @@
       <c r="B14" s="3" t="n"/>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="5" t="n">
-        <v>545748574</v>
+        <v>548015539</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>HF537684538</t>
+          <t>HF537685966</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/21/2026</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>United Healthcare</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>United Healthcare</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K14" s="4" t="n"/>
@@ -2495,7 +2487,7 @@
         <v/>
       </c>
       <c r="M14" s="7" t="n">
-        <v>46121</v>
+        <v>46133</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
@@ -2504,7 +2496,7 @@
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>UHC COMMERCIAL</t>
+          <t>BCBS</t>
         </is>
       </c>
       <c r="P14" s="6" t="n"/>
@@ -2514,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U14" s="8" t="n">
         <v>0</v>
@@ -2524,18 +2516,18 @@
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
-          <t>04/29/2026</t>
+          <t>02/11/2026</t>
         </is>
       </c>
       <c r="X14" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="Z14" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F330</t>
         </is>
       </c>
       <c r="AA14" s="6" t="n"/>
@@ -2544,12 +2536,12 @@
       <c r="AD14" s="5" t="n"/>
       <c r="AE14" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF14" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG14" s="6" t="inlineStr">
@@ -2562,9 +2554,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI14" s="9" t="n"/>
+      <c r="AI14" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
+        </is>
+      </c>
       <c r="AJ14" s="5" t="n">
-        <v>52</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15">
@@ -2572,36 +2568,36 @@
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="5" t="n">
-        <v>556348109</v>
+        <v>548015539</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>HF434792716</t>
+          <t>HF537685966</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>01/14/2026</t>
+          <t>01/21/2026</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K15" s="4" t="n"/>
@@ -2610,7 +2606,7 @@
         <v/>
       </c>
       <c r="M15" s="7" t="n">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
@@ -2619,7 +2615,7 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>BCBS</t>
         </is>
       </c>
       <c r="P15" s="6" t="n"/>
@@ -2629,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>976.64</v>
+        <v>1029.98</v>
       </c>
       <c r="U15" s="8" t="n">
         <v>0</v>
@@ -2639,18 +2635,18 @@
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>02/11/2026</t>
         </is>
       </c>
       <c r="X15" s="8" t="n">
-        <v>976.64</v>
+        <v>1029.98</v>
       </c>
       <c r="Y15" s="5" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
+          <t>F330</t>
         </is>
       </c>
       <c r="AA15" s="6" t="n"/>
@@ -2677,46 +2673,54 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI15" s="9" t="n"/>
+      <c r="AI15" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
+        </is>
+      </c>
       <c r="AJ15" s="5" t="n">
-        <v>715</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="5" t="n">
-        <v>548015539</v>
+        <v>547442681</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>HF537685966</t>
+          <t>HF359780591</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>01/21/2026</t>
+          <t>01/22/2026</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
+          <t>TRIADA GAP BENEFITS</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>TRIADA GAP BENEFITS</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K16" s="4" t="n"/>
@@ -2725,7 +2729,7 @@
         <v/>
       </c>
       <c r="M16" s="7" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
@@ -2744,34 +2748,36 @@
         <v>1</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>0</v>
+        <v>840.66</v>
       </c>
       <c r="V16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="W16" s="6" t="inlineStr">
         <is>
-          <t>02/11/2026</t>
+          <t>03/13/2026</t>
         </is>
       </c>
       <c r="X16" s="8" t="n">
-        <v>396.27</v>
+        <v>135.98</v>
       </c>
       <c r="Y16" s="5" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Z16" s="6" t="inlineStr">
         <is>
-          <t>F330</t>
+          <t>F411</t>
         </is>
       </c>
       <c r="AA16" s="6" t="n"/>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
-      <c r="AD16" s="5" t="n"/>
+      <c r="AD16" s="5" t="n">
+        <v>556556161</v>
+      </c>
       <c r="AE16" s="6" t="inlineStr">
         <is>
           <t>LEATHEM, JARRETT</t>
@@ -2779,12 +2785,12 @@
       </c>
       <c r="AF16" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG16" s="6" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="AH16" s="6" t="inlineStr">
@@ -2794,11 +2800,11 @@
       </c>
       <c r="AI16" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ16" s="5" t="n">
-        <v>358</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17">
@@ -2806,16 +2812,16 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="5" t="n">
-        <v>548015539</v>
+        <v>555599776</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>HF537685966</t>
+          <t>HF475536429</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>01/21/2026</t>
+          <t>01/27/2026</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -2830,7 +2836,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -2844,7 +2850,7 @@
         <v/>
       </c>
       <c r="M17" s="7" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
@@ -2873,18 +2879,18 @@
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>02/11/2026</t>
+          <t>04/16/2026</t>
         </is>
       </c>
       <c r="X17" s="8" t="n">
         <v>1029.98</v>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="Z17" s="6" t="inlineStr">
         <is>
-          <t>F330</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA17" s="6" t="n"/>
@@ -2893,12 +2899,12 @@
       <c r="AD17" s="5" t="n"/>
       <c r="AE17" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>O'NEIL, ROY</t>
         </is>
       </c>
       <c r="AF17" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG17" s="6" t="inlineStr">
@@ -2913,37 +2919,33 @@
       </c>
       <c r="AI17" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
-        <v>359</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="n"/>
       <c r="B18" s="3" t="n"/>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="5" t="n">
-        <v>547442681</v>
+        <v>555599776</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>HF359780591</t>
+          <t>HF475536429</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>01/22/2026</t>
+          <t>01/27/2026</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>TRIADA GAP BENEFITS</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -2953,12 +2955,12 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>TRIADA GAP BENEFITS</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K18" s="4" t="n"/>
@@ -2967,7 +2969,7 @@
         <v/>
       </c>
       <c r="M18" s="7" t="n">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
@@ -2986,49 +2988,47 @@
         <v>1</v>
       </c>
       <c r="T18" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U18" s="8" t="n">
-        <v>840.66</v>
+        <v>0</v>
       </c>
       <c r="V18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="W18" s="6" t="inlineStr">
         <is>
-          <t>03/13/2026</t>
+          <t>04/16/2026</t>
         </is>
       </c>
       <c r="X18" s="8" t="n">
-        <v>135.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y18" s="5" t="n">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="Z18" s="6" t="inlineStr">
         <is>
-          <t>F411</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA18" s="6" t="n"/>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
-      <c r="AD18" s="5" t="n">
-        <v>556556161</v>
-      </c>
+      <c r="AD18" s="5" t="n"/>
       <c r="AE18" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>O'NEIL, ROY</t>
         </is>
       </c>
       <c r="AF18" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG18" s="6" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="AH18" s="6" t="inlineStr">
@@ -3038,11 +3038,11 @@
       </c>
       <c r="AI18" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
-        <v>158</v>
+        <v>714</v>
       </c>
     </row>
     <row r="19">
@@ -3050,11 +3050,11 @@
       <c r="B19" s="3" t="n"/>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="5" t="n">
-        <v>555599776</v>
+        <v>556349314</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>HF475536429</t>
+          <t>HF431164004</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K19" s="4" t="n"/>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>BCBS</t>
+          <t>OPTUM</t>
         </is>
       </c>
       <c r="P19" s="6" t="n"/>
@@ -3107,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="T19" s="8" t="n">
-        <v>1029.98</v>
+        <v>976.64</v>
       </c>
       <c r="U19" s="8" t="n">
         <v>0</v>
@@ -3117,21 +3117,25 @@
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>04/16/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="X19" s="8" t="n">
-        <v>1029.98</v>
+        <v>976.64</v>
       </c>
       <c r="Y19" s="5" t="n">
         <v>193</v>
       </c>
       <c r="Z19" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
-        </is>
-      </c>
-      <c r="AA19" s="6" t="n"/>
+          <t>F331</t>
+        </is>
+      </c>
+      <c r="AA19" s="6" t="inlineStr">
+        <is>
+          <t>F411</t>
+        </is>
+      </c>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
       <c r="AD19" s="5" t="n"/>
@@ -3142,12 +3146,12 @@
       </c>
       <c r="AF19" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Goodyear</t>
         </is>
       </c>
       <c r="AG19" s="6" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="AH19" s="6" t="inlineStr">
@@ -3155,13 +3159,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI19" s="9" t="inlineStr">
-        <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
-        </is>
-      </c>
+      <c r="AI19" s="9" t="n"/>
       <c r="AJ19" s="5" t="n">
-        <v>713</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20">
@@ -3169,16 +3169,16 @@
       <c r="B20" s="3" t="n"/>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="5" t="n">
-        <v>555599776</v>
+        <v>547976909</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>HF475536429</t>
+          <t>HF535417942</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>01/27/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>LIEN 05</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K20" s="4" t="n"/>
@@ -3207,7 +3207,7 @@
         <v/>
       </c>
       <c r="M20" s="7" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="T20" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U20" s="8" t="n">
         <v>0</v>
@@ -3236,18 +3236,18 @@
       </c>
       <c r="W20" s="6" t="inlineStr">
         <is>
-          <t>04/16/2026</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="X20" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="Y20" s="5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="Z20" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F4323</t>
         </is>
       </c>
       <c r="AA20" s="6" t="n"/>
@@ -3256,17 +3256,17 @@
       <c r="AD20" s="5" t="n"/>
       <c r="AE20" s="6" t="inlineStr">
         <is>
-          <t>O'NEIL, ROY</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF20" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG20" s="6" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="AH20" s="6" t="inlineStr">
@@ -3276,11 +3276,11 @@
       </c>
       <c r="AI20" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
-        <v>714</v>
+        <v>666</v>
       </c>
     </row>
     <row r="21">
@@ -3288,26 +3288,26 @@
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="5" t="n">
-        <v>556349314</v>
+        <v>557090486</v>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>HF431164004</t>
+          <t>HF342585384</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>01/27/2026</t>
+          <t>01/14/2026</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K21" s="4" t="n"/>
@@ -3326,26 +3326,26 @@
         <v/>
       </c>
       <c r="M21" s="7" t="n">
-        <v>46139</v>
+        <v>46156</v>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>90 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P21" s="6" t="n"/>
       <c r="Q21" s="6" t="n"/>
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T21" s="8" t="n">
-        <v>976.64</v>
+        <v>792.54</v>
       </c>
       <c r="U21" s="8" t="n">
         <v>0</v>
@@ -3355,36 +3355,32 @@
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>03/17/2026</t>
         </is>
       </c>
       <c r="X21" s="8" t="n">
-        <v>976.64</v>
+        <v>792.54</v>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="Z21" s="6" t="inlineStr">
         <is>
-          <t>F331</t>
-        </is>
-      </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>F411</t>
-        </is>
-      </c>
+          <t>F332</t>
+        </is>
+      </c>
+      <c r="AA21" s="6" t="n"/>
       <c r="AB21" s="6" t="n"/>
       <c r="AC21" s="6" t="n"/>
       <c r="AD21" s="5" t="n"/>
       <c r="AE21" s="6" t="inlineStr">
         <is>
-          <t>O'NEIL, ROY</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF21" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Goodyear</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG21" s="6" t="inlineStr">
@@ -3397,9 +3393,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI21" s="9" t="n"/>
+      <c r="AI21" s="9" t="inlineStr">
+        <is>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
+        </is>
+      </c>
       <c r="AJ21" s="5" t="n">
-        <v>471</v>
+        <v>638</v>
       </c>
     </row>
     <row r="22">
@@ -3407,31 +3407,31 @@
       <c r="B22" s="3" t="n"/>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="5" t="n">
-        <v>547976909</v>
+        <v>557090486</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>HF535417942</t>
+          <t>HF342585384</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>01/14/2026</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>LIEN 05</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
@@ -3445,16 +3445,16 @@
         <v/>
       </c>
       <c r="M22" s="7" t="n">
-        <v>46141</v>
+        <v>46156</v>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>90 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t>BCBS</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P22" s="6" t="n"/>
@@ -3474,18 +3474,18 @@
       </c>
       <c r="W22" s="6" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>03/17/2026</t>
         </is>
       </c>
       <c r="X22" s="8" t="n">
         <v>976.64</v>
       </c>
       <c r="Y22" s="5" t="n">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="Z22" s="6" t="inlineStr">
         <is>
-          <t>F4323</t>
+          <t>F332</t>
         </is>
       </c>
       <c r="AA22" s="6" t="n"/>
@@ -3514,11 +3514,11 @@
       </c>
       <c r="AI22" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
-        <v>666</v>
+        <v>639</v>
       </c>
     </row>
     <row r="23">
@@ -3526,26 +3526,26 @@
       <c r="B23" s="3" t="n"/>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="5" t="n">
-        <v>557090486</v>
+        <v>565238310</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>HF342585384</t>
+          <t>HF524312806</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>01/14/2026</t>
+          <t>01/23/2026</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K23" s="4" t="n"/>
@@ -3564,7 +3564,7 @@
         <v/>
       </c>
       <c r="M23" s="7" t="n">
-        <v>46216</v>
+        <v>46225</v>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
@@ -3573,17 +3573,17 @@
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>MEDICA</t>
         </is>
       </c>
       <c r="P23" s="6" t="n"/>
       <c r="Q23" s="6" t="n"/>
       <c r="R23" s="6" t="n"/>
       <c r="S23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>792.54</v>
+        <v>1029.98</v>
       </c>
       <c r="U23" s="8" t="n">
         <v>0</v>
@@ -3593,18 +3593,18 @@
       </c>
       <c r="W23" s="6" t="inlineStr">
         <is>
-          <t>03/17/2026</t>
+          <t>02/17/2026</t>
         </is>
       </c>
       <c r="X23" s="8" t="n">
-        <v>792.54</v>
+        <v>1029.98</v>
       </c>
       <c r="Y23" s="5" t="n">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="Z23" s="6" t="inlineStr">
         <is>
-          <t>F332</t>
+          <t>F411</t>
         </is>
       </c>
       <c r="AA23" s="6" t="n"/>
@@ -3613,17 +3613,17 @@
       <c r="AD23" s="5" t="n"/>
       <c r="AE23" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF23" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG23" s="6" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="AH23" s="6" t="inlineStr">
@@ -3631,9 +3631,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI23" s="9" t="n"/>
+      <c r="AI23" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 180 days from DOS; 180 days from the Medicare payment date for Select Solution and Prime Solution.</t>
+        </is>
+      </c>
       <c r="AJ23" s="5" t="n">
-        <v>638</v>
+        <v>540</v>
       </c>
     </row>
     <row r="24">
@@ -3641,26 +3645,26 @@
       <c r="B24" s="3" t="n"/>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="5" t="n">
-        <v>557090486</v>
+        <v>565238310</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>HF342585384</t>
+          <t>HF524312806</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>01/14/2026</t>
+          <t>01/23/2026</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -3670,7 +3674,7 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K24" s="4" t="n"/>
@@ -3679,7 +3683,7 @@
         <v/>
       </c>
       <c r="M24" s="7" t="n">
-        <v>46216</v>
+        <v>46225</v>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -3688,7 +3692,7 @@
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>MEDICA</t>
         </is>
       </c>
       <c r="P24" s="6" t="n"/>
@@ -3698,7 +3702,7 @@
         <v>1</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U24" s="8" t="n">
         <v>0</v>
@@ -3708,18 +3712,18 @@
       </c>
       <c r="W24" s="6" t="inlineStr">
         <is>
-          <t>03/17/2026</t>
+          <t>02/17/2026</t>
         </is>
       </c>
       <c r="X24" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y24" s="5" t="n">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="Z24" s="6" t="inlineStr">
         <is>
-          <t>F332</t>
+          <t>F411</t>
         </is>
       </c>
       <c r="AA24" s="6" t="n"/>
@@ -3728,17 +3732,17 @@
       <c r="AD24" s="5" t="n"/>
       <c r="AE24" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF24" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG24" s="6" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="AH24" s="6" t="inlineStr">
@@ -3746,9 +3750,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI24" s="9" t="n"/>
+      <c r="AI24" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 180 days from DOS; 180 days from the Medicare payment date for Select Solution and Prime Solution.</t>
+        </is>
+      </c>
       <c r="AJ24" s="5" t="n">
-        <v>639</v>
+        <v>541</v>
       </c>
     </row>
     <row r="25">
@@ -3756,26 +3764,26 @@
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="5" t="n">
-        <v>565238310</v>
+        <v>566830437</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>HF524312806</t>
+          <t>HF453012792</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>01/23/2026</t>
+          <t>01/28/2026</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
+          <t>Health Choice Arizona</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
+          <t>Health Choice Arizona</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -3785,7 +3793,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K25" s="4" t="n"/>
@@ -3793,11 +3801,17 @@
         <f>IF($M25="","",$M25-TODAY())</f>
         <v/>
       </c>
-      <c r="M25" s="7" t="n"/>
-      <c r="N25" s="6" t="n"/>
+      <c r="M25" s="7" t="n">
+        <v>46230</v>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>180 days</t>
+        </is>
+      </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>MEDICA</t>
+          <t>HEALTH CHOICE MEDICAID</t>
         </is>
       </c>
       <c r="P25" s="6" t="n"/>
@@ -3807,7 +3821,7 @@
         <v>1</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U25" s="8" t="n">
         <v>0</v>
@@ -3817,14 +3831,14 @@
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
-          <t>02/17/2026</t>
+          <t>06/25/2026</t>
         </is>
       </c>
       <c r="X25" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y25" s="5" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="Z25" s="6" t="inlineStr">
         <is>
@@ -3837,7 +3851,7 @@
       <c r="AD25" s="5" t="n"/>
       <c r="AE25" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF25" s="6" t="inlineStr">
@@ -3847,7 +3861,7 @@
       </c>
       <c r="AG25" s="6" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/15/2026</t>
         </is>
       </c>
       <c r="AH25" s="6" t="inlineStr">
@@ -3855,9 +3869,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI25" s="9" t="n"/>
+      <c r="AI25" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 6 months (not primary) or 7 months (primary). The reference converts months at 30 days, so the real deadline may fall a few days later - count calendar months where it matters.</t>
+        </is>
+      </c>
       <c r="AJ25" s="5" t="n">
-        <v>540</v>
+        <v>939</v>
       </c>
     </row>
     <row r="26">
@@ -3865,26 +3883,26 @@
       <c r="B26" s="3" t="n"/>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="5" t="n">
-        <v>565238310</v>
+        <v>566830437</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>HF524312806</t>
+          <t>HF453012792</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>01/23/2026</t>
+          <t>01/28/2026</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
+          <t>Health Choice Arizona</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
+          <t>Health Choice Arizona</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -3894,7 +3912,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K26" s="4" t="n"/>
@@ -3902,11 +3920,17 @@
         <f>IF($M26="","",$M26-TODAY())</f>
         <v/>
       </c>
-      <c r="M26" s="7" t="n"/>
-      <c r="N26" s="6" t="n"/>
+      <c r="M26" s="7" t="n">
+        <v>46230</v>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>180 days</t>
+        </is>
+      </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>MEDICA</t>
+          <t>HEALTH CHOICE MEDICAID</t>
         </is>
       </c>
       <c r="P26" s="6" t="n"/>
@@ -3916,7 +3940,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U26" s="8" t="n">
         <v>0</v>
@@ -3926,14 +3950,14 @@
       </c>
       <c r="W26" s="6" t="inlineStr">
         <is>
-          <t>02/17/2026</t>
+          <t>06/25/2026</t>
         </is>
       </c>
       <c r="X26" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="Y26" s="5" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="Z26" s="6" t="inlineStr">
         <is>
@@ -3946,7 +3970,7 @@
       <c r="AD26" s="5" t="n"/>
       <c r="AE26" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF26" s="6" t="inlineStr">
@@ -3956,7 +3980,7 @@
       </c>
       <c r="AG26" s="6" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/15/2026</t>
         </is>
       </c>
       <c r="AH26" s="6" t="inlineStr">
@@ -3964,9 +3988,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI26" s="9" t="n"/>
+      <c r="AI26" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 6 months (not primary) or 7 months (primary). The reference converts months at 30 days, so the real deadline may fall a few days later - count calendar months where it matters.</t>
+        </is>
+      </c>
       <c r="AJ26" s="5" t="n">
-        <v>541</v>
+        <v>940</v>
       </c>
     </row>
   </sheetData>
@@ -4972,7 +5000,7 @@
       </c>
       <c r="AI7" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
@@ -9645,7 +9673,7 @@
       </c>
       <c r="AI33" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ33" s="5" t="n">
@@ -9776,7 +9804,7 @@
       </c>
       <c r="AI34" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ34" s="5" t="n">
@@ -9903,7 +9931,7 @@
       </c>
       <c r="AI35" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ35" s="5" t="n">
@@ -10034,7 +10062,7 @@
       </c>
       <c r="AI36" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ36" s="5" t="n">
@@ -10165,7 +10193,7 @@
       </c>
       <c r="AI37" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ37" s="5" t="n">
@@ -10292,7 +10320,7 @@
       </c>
       <c r="AI38" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ38" s="5" t="n">
@@ -10427,7 +10455,7 @@
       </c>
       <c r="AI39" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ39" s="5" t="n">
@@ -10558,7 +10586,7 @@
       </c>
       <c r="AI40" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ40" s="5" t="n">
@@ -10685,7 +10713,7 @@
       </c>
       <c r="AI41" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ41" s="5" t="n">
@@ -10816,7 +10844,7 @@
       </c>
       <c r="AI42" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ42" s="5" t="n">
@@ -10947,7 +10975,7 @@
       </c>
       <c r="AI43" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ43" s="5" t="n">
@@ -11082,7 +11110,7 @@
       </c>
       <c r="AI44" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ44" s="5" t="n">
@@ -11213,7 +11241,7 @@
       </c>
       <c r="AI45" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ45" s="5" t="n">
@@ -11340,7 +11368,7 @@
       </c>
       <c r="AI46" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ46" s="5" t="n">
@@ -11475,7 +11503,7 @@
       </c>
       <c r="AI47" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ47" s="5" t="n">
@@ -11598,7 +11626,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI48" s="9" t="n"/>
+      <c r="AI48" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ48" s="5" t="n">
         <v>360</v>
       </c>
@@ -11715,7 +11747,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI49" s="9" t="n"/>
+      <c r="AI49" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ49" s="5" t="n">
         <v>361</v>
       </c>
@@ -11832,7 +11868,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI50" s="9" t="n"/>
+      <c r="AI50" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ50" s="5" t="n">
         <v>362</v>
       </c>
@@ -11953,7 +11993,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI51" s="9" t="n"/>
+      <c r="AI51" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ51" s="5" t="n">
         <v>363</v>
       </c>
@@ -12078,7 +12122,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI52" s="9" t="n"/>
+      <c r="AI52" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ52" s="5" t="n">
         <v>364</v>
       </c>
@@ -12203,7 +12251,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI53" s="9" t="n"/>
+      <c r="AI53" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ53" s="5" t="n">
         <v>365</v>
       </c>
@@ -12324,7 +12376,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI54" s="9" t="n"/>
+      <c r="AI54" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ54" s="5" t="n">
         <v>385</v>
       </c>
@@ -12818,7 +12874,7 @@
       </c>
       <c r="AI3" s="9" t="inlineStr">
         <is>
-          <t>Matched to the Cigna row by carrier name; the reference lists only the HealthSpring / Cigna Medicare Advantage variants in column F.</t>
+          <t>Limit as stated: 90 days from DOS. Matched to the Cigna row by carrier name; the reference lists only the HealthSpring / Cigna Medicare Advantage variants.</t>
         </is>
       </c>
       <c r="AJ3" s="5" t="n">
@@ -13177,7 +13233,7 @@
       </c>
       <c r="AI6" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ6" s="5" t="n">
@@ -13306,7 +13362,7 @@
       </c>
       <c r="AI7" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
@@ -13425,7 +13481,7 @@
       </c>
       <c r="AI8" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
@@ -14169,7 +14225,7 @@
       </c>
       <c r="AI2" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ2" s="5" t="n">
@@ -14409,7 +14465,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI4" s="9" t="n"/>
+      <c r="AI4" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ4" s="5" t="n">
         <v>85</v>
       </c>
@@ -14540,7 +14600,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI5" s="9" t="n"/>
+      <c r="AI5" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ5" s="5" t="n">
         <v>601</v>
       </c>
@@ -14782,7 +14846,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI7" s="9" t="n"/>
+      <c r="AI7" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ7" s="5" t="n">
         <v>941</v>
       </c>
@@ -15003,7 +15071,7 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2 - Due in 6-30 days: 2</t>
+          <t xml:space="preserve">    2 - Due in 6-30 days: 0</t>
         </is>
       </c>
     </row>
@@ -15017,14 +15085,14 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4 - Past deadline: 46</t>
+          <t xml:space="preserve">    4 - Past deadline: 50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5 - No limit on file: 12</t>
+          <t xml:space="preserve">    5 - No limit on file: 10</t>
         </is>
       </c>
     </row>

--- a/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
@@ -27,10 +27,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="MM/DD/YYYY"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -127,7 +126,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,12 +281,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -332,12 +331,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -382,12 +381,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -432,12 +431,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -482,12 +481,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -15014,7 +15013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -15154,7 +15153,7 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "25/06/2026";  Date Worked 1: "12/08/2026".</t>
+          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
         </is>
       </c>
     </row>
@@ -15171,46 +15170,39 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Both are real dates displayed DD/MM/YYYY. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
+          <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Careful when typing into them: Excel reads what you type using its own date setting, not the DD/MM/YYYY the cell displays. On a US Excel, typing 06/25/2026 gives 25 June and the cell then shows 25/06/2026. Type the date the way your Excel expects it and let the cell do the formatting, or check the formula bar afterwards. Every other date column in these files is MM/DD/YYYY, as in the source data.</t>
-        </is>
-      </c>
+      <c r="A26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr"/>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>How this file feeds the master</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>How this file feeds the master</t>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
-        </is>
-      </c>
+      <c r="A30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Everything else in this file is a static copy of the source data from 'Specialty Claims Pending 2026-S1.xlsx' (sheet 'Merged').</t>
         </is>
